--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -693,7 +693,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -707,7 +711,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính số request lỗi cho phép và thực tế trên cùng mẫu số.</t>
+          <t>Tổng số 10.000 requests với SLO 99,7% cho phép tối đa: 10.000 * (100% - 99,7%) = 10.000 * 0,003 = 30 request lỗi. Số request lỗi thực tế: 10.000 - 9.950 = 50 request. Số request vượt quá error budget = 50 - 30 = 20 request.</t>
         </is>
       </c>
     </row>
@@ -843,7 +847,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cần biết inject gì, ở đâu, mong đợi gì và lúc nào dừng.</t>
+          <t>Thí nghiệm Chaos Engineering có kiểm soát đòi hỏi: (a) Giới hạn phạm vi tiêm lỗi (blast radius) tại staging/canary, (b) xác định rõ hành vi kỳ vọng và ngưỡng SLI, (c) thiết lập telemetry đo lường, điều kiện tự động dừng (abort conditions) và kiểm chứng khả năng tự hồi phục.</t>
         </is>
       </c>
     </row>
@@ -931,7 +935,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn field phục vụ query/trace nhưng không trở thành data exposure.</t>
+          <t>Logging có cấu trúc an toàn trong hệ thống phân tán: (a) Ghi timestamp, event_name, request/trace ID, (b) ghi latency từng chặng, status, số token/cost và error code an toàn, (c) định dạng JSON một dòng và che giấu/bảo vệ dữ liệu định danh người dùng.</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1351,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lọc ứng viên không hợp policy trước, rồi mới xét health hoặc chi phí.</t>
+          <t>Quy tắc định tuyến dự phòng (failover routing): (a) Lọc ứng viên theo năng lực kỹ thuật, quy định vùng dữ liệu (data residency), phân quyền và ngân sách trước, (b) chỉ route tới model tương thích hợp đồng API và đang sẵn sàng, (c) trả lỗi có kiểm soát hoặc degraded outcome khi không còn ứng viên hợp lệ.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -672,10 +672,27 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Thiết lập ngân sách độ trễ (Latency Budget) và Timeout chuẩn xác cho cả 3 thành phần: Payment (3s), Model (15s), Search (1.5s).
+- [1.5 điểm] Thiết kế phân vùng Bulkhead cách ly hoàn toàn tài nguyên (Connection Pools / Thread Pools) giữa 3 dịch vụ.
+- [1.5 điểm] Dự đoán chuẩn xác khả năng phục vụ khi có sự cố: Search sập thì Payment và Model vẫn phục vụ trơn tru ở chế độ degraded mode.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Ngân sách Độ trễ (Latency Budgets) và Phân vùng Bulkhead (Bulkhead Isolation):
+   - Phân tích: Đồ thị cuộc gọi gồm 3 thành phần có đặc tính độ trễ hoàn toàn khác biệt: Payment (thao tác tài chính quan trọng), Model/LLM (sinh token độ trễ cao) và Search (tra cứu thông tin mở rộng).
+   - Thiết lập Latency Budget và Timeout độc lập cho từng dịch vụ:
+     + Dịch vụ Payment (Nghiệp vụ Trọng yếu - Zero Tolerance): Timeout ngắn và dứt khoát: `timeout = 3.0` giây. Phân vùng Bulkhead riêng với Worker Pool độc lập (ví dụ: 10 dedicated connections).
+     + Dịch vụ Model/LLM (Tác vụ Tính toán Nặng): Timeout dài: `timeout = 15.0` giây để cho phép mô hình sinh xong các đoạn văn bản dài. Phân vùng Bulkhead riêng biệt (ví dụ: 25 dedicated async workers).
+     + Dịch vụ Search (Tra cứu Mở rộng - Non-Critical): Timeout ngắn: `timeout = 1.5` giây. Phân vùng Bulkhead riêng biệt (ví dụ: 15 dedicated HTTP client sockets).
+   - Nguyên tắc Bulkhead: Phân tách rạch ròi Connection Pools, Thread Pools và Memory Queues giữa 3 dịch vụ; sự cố cạn kiệt tài nguyên ở dịch vụ này tuyệt đối không thể lây nhiễm làm nghẽn dịch vụ khác.
+2. Dự đoán Khả năng Phục vụ của Các Workload khi Xảy ra Sự cố (Fault Isolation Prediction):
+   - Tình huống Dịch vụ Search bị Nghẽn hoặc Sập Hoàn toàn (Search Latency tăng vọt lên 30s hoặc Timeout 100%):
+     + Nhờ Timeout 1.5s, các yêu cầu Search bị ngắt mạch nhanh chóng (Fail-Fast).
+     + Do Search nằm trong Bulkhead riêng, nó KHÔNG HỀ chiếm dụng bất kỳ connection nào của Payment hay Model.
+     + Workload VẪN PHỤC VỤ HOÀN TOÀN BÌNH THƯỜNG: Hệ thống kích hoạt cơ chế Suy giảm Duyên dáng (Graceful Degradation): Luồng thanh toán Payment vẫn thực hiện trơn tru 100%, luồng chat Model vẫn trả về câu trả lời cho người dùng (chỉ thiếu phần trích dẫn từ kết quả search).
+   - Tình huống Dịch vụ Model bị Nghẽn: Workload Payment độc lập vẫn tiếp tục xử lý các giao dịch thanh toán bình thường mà không bị ảnh hưởng dây chuyền.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mẫu thiết kế Vách ngăn Kín nước (Bulkhead Pattern) lấy cảm hứng từ cấu trúc phân khoang của thân tàu thủy nhằm ngăn một khoang bị thủng làm chìm toàn bộ con tàu. Bằng cách gán ngân sách độ trễ riêng và phân bổ tài nguyên độc lập cho từng thành phần trong đồ thị cuộc gọi, hệ thống bảo vệ toàn vẹn các chức năng sống còn (như Payment) ngay cả khi các dịch vụ phụ trợ gặp sự cố nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Michael T. Nygard - Release It! (Bulkheads Pattern) &amp; Microsoft Azure Architecture Patterns - Bulkhead Pattern</t>
         </is>
       </c>
     </row>
@@ -742,10 +759,36 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Phân biệt rõ ràng giữa SLO nội bộ (99.7% không phạt) và SLA bên ngoài (99.0% cam kết pháp lý kèm mức phạt).
+- [1.5 điểm] Tính toán chính xác SLI thực tế đạt 99.50% và khẳng định tuân thủ thành công SLA (không bị phạt hợp đồng).
+- [1.5 điểm] Tính toán chính xác trạng thái Error Budget bị âm (cho phép 30 lỗi, thực tế 50 lỗi, burn 166.7%) và nêu hành động đóng băng tính năng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân biệt Mục tiêu Nội bộ (SLO) với Cam kết Pháp lý Bên ngoài (SLA):
+   - SLI Thực tế Đo lường được (Service Level Indicator):
+     Trong 10.000 yêu cầu hợp lệ, có 9.950 yêu cầu đạt độ trễ $\le 2$ giây.
+     `SLI = (9.950 / 10.000) * 100% = 99.50%`.
+   - Mục tiêu Nội bộ (Internal SLO = 99.70%):
+     Là mục tiêu kỹ thuật phấn đấu do đội ngũ kỹ thuật nội bộ tự đặt ra để đảm bảo chất lượng dịch vụ cao nhất và tạo biên độ đệm an toàn. Mục tiêu này KHÔNG đi kèm mức phạt tài chính, mà là kim chỉ nam để điều tiết tốc độ phát triển tính năng.
+   - Cam kết Bên ngoài (External SLA = 99.00%):
+     Là điều khoản cam kết dịch vụ mang tính pháp lý trong hợp đồng với khách hàng. Nếu SLI thực tế rơi xuống dưới mức 99.00%, doanh nghiệp phải chịu trách nhiệm bồi thường tài chính (Service Credits / Penalty). Mức SLA luôn được đặt thấp hơn SLO để tạo khoảng đệm an toàn bảo vệ doanh nghiệp.
+2. Đánh giá Trạng thái Tuân thủ và Tính toán Ngân sách Lỗi (Error Budget Calculation):
+   - Đánh giá Cam kết SLA Khách hàng:
+     `SLI Thực tế (99.50%) &gt; SLA Cam kết (99.00%)`.
+     -&gt; Kết luận: DOANH NGHIỆP TUÂN THỦ HOÀN TOÀN CAM KẾT SLA, KHÔNG BỊ PHẠT HỢP ĐỒNG.
+   - Đánh giá Mục tiêu Nội bộ SLO và Tính toán Error Budget:
+     `SLI Thực tế (99.50%) &lt; SLO Nội bộ (99.70%)`.
+     -&gt; Kết luận: VI PHẠM MỤC TIÊU NỘI BỘ, ĐÃ ĐỐT CHÁY QUÁ NGÂN SÁCH LỖI CHO PHÉP.
+     + Tổng số yêu cầu lỗi tối đa cho phép theo SLO (99.7%): `10.000 * (1 - 0.997) = 30` yêu cầu.
+     + Số lượng yêu cầu vi phạm độ trễ thực tế: `10.000 - 9.950 = 50` yêu cầu.
+     + Tỷ lệ đốt ngân sách lỗi (Error Budget Burn):
+       `Burn Rate = 50 / 30 = 166.67%`.
+     + Trạng thái Ngân sách Lỗi: BỊ ÂM HOÀN TOÀN (Vượt quá ngân sách lỗi cho phép 20 yêu cầu, tức âm 66.67% ngân sách).
+   - Hành động Quản trị Kỹ thuật (SRE Policy Action):
+     Kích hoạt chính sách đóng băng triển khai tính năng mới (Feature Freeze). Đội ngũ kỹ thuật chuyển 100% trọng tâm sang việc tối ưu hóa hiệu năng, giảm độ trễ P95/P99 để bù đắp lại ngân sách lỗi trong chu kỳ tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong phương pháp luận SRE, việc phân định ranh giới giữa SLA pháp lý và SLO nội bộ là công cụ quản trị rủi ro tối quan trọng. SLO khắt khe hơn SLA tạo ra một khoảng đệm an toàn giúp đội ngũ kỹ thuật chủ động phát hiện sự suy giảm chất lượng và hành động trước khi hệ thống chạm ngưỡng vi phạm hợp đồng phải bồi thường thiệt hại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Site Reliability Engineering (SRE) Book - Service Level Objectives: https://sre.google/sre-book/service-level-objectives/ và The Site Reliability Workbook</t>
         </is>
       </c>
     </row>
@@ -878,10 +921,31 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Xây dựng giả định kiểm chứng rõ ràng và thiết lập kiểm soát phạm vi ảnh hưởng (Blast Radius) chặt chẽ.
+- [1.5 điểm] Thiết kế kịch bản tiêm lỗi cụ thể (tiêm latency 15s / HTTP 504) bằng Toxiproxy hoặc Chaos Mesh.
+- [1.5 điểm] Xác định rõ các chỉ số giám sát cốt lõi của Payment và thiết lập cơ chế dừng khẩn cấp (Emergency Abort) tự động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Thí nghiệm Hỗn loạn có Kiểm soát (Controlled Chaos Engineering Experiment):
+   - Nhận định cần kiểm chứng (Hypothesis): 'Sự cố suy giảm hiệu năng hoặc chậm trễ nghiêm trọng của dịch vụ Search không được phép làm gián đoạn hay ảnh hưởng tới tính khả dụng của dịch vụ Thanh toán (Payment).'
+   - Kiểm soát Phạm vi Ảnh hưởng (Blast Radius Control):
+     Thí nghiệm được thực thi trên môi trường Pre-Production / Staging có lưu lượng tải mô phỏng, hoặc trên một tập hợp lưu lượng thử nghiệm nhỏ (1-2% synthetic canary traffic) trên production có gắn cờ thử nghiệm.
+   - Kịch bản Tiêm Lỗi (Fault Injection Scenario):
+     Sử dụng công cụ tiêm lỗi chuyên dụng (như Chaos Mesh, Toxiproxy hoặc Envoy Fault Injection Filter) can thiệp vào tầng mạng của Search Service:
+     + Tiêm độ trễ mạng nhân tạo: Thêm 15.000ms (15 giây) vào 100% các yêu cầu gửi tới Search Service.
+     + Tiêm lỗi sập kết nối: Giả lập Search Service trả về mã phản hồi `HTTP 504 Gateway Timeout`.
+2. Giám sát Chỉ số và Điều kiện Hủy Bỏ Khẩn cấp (Observability &amp; Emergency Abort Conditions):
+   - Chỉ số Giám sát Trọng yếu (Steady-State Metrics):
+     + `payment_success_rate`: Tỷ lệ thành công của dịch vụ Payment (Kỳ vọng: Giữ vững $\ge 99.99\%$).
+     + `payment_latency_p99`: Độ trễ P99 của Payment (Kỳ vọng: Không tăng quá 5% so với mức cơ sở bình thường).
+     + `search_timeout_count`: Số lượng cuộc gọi search bị timeout ngắt mạch thành công.
+   - Điều kiện Dừng Khẩn cấp (Emergency Abort Threshold):
+     Nếu tại bất kỳ thời điểm nào tỷ lệ thành công của Payment giảm xuống dưới 99.5% hoặc độ trễ Payment P99 tăng quá 20%, hệ thống tự động kích hoạt ngắt thí nghiệm (Auto-Rollback) trong vòng dưới 3 giây.
+3. Kết luận và Tiêu chí Đánh giá Thành công:
+   - Thí nghiệm thành công khi: Search Service bị tắc nghẽn 15s nhưng hệ thống ngắt mạch sớm tại 1.5s, giao diện người dùng hiển thị thông báo giảm cấp nhẹ (degraded), và 100% các giao dịch Payment được hoàn tất trơn tru.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thực hành Chaos Engineering có kiểm soát là phương pháp khoa học duy nhất để xác thực khả năng tự phục hồi và tính cô lập lỗi của kiến trúc phân tán. Bằng cách chủ động tiêm độ trễ vào các thành phần phi trọng yếu (như Search) dưới sự kiểm soát chặt chẽ của cơ chế dừng khẩn cấp, doanh nghiệp bảo đảm rằng các chức năng huyết mạch (như Payment) sẽ không bao giờ sụp đổ dây chuyền trong thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Principles of Chaos Engineering: https://principlesofchaos.org/ và Netflix Chaos Engineering Architecture Guide</t>
         </is>
       </c>
     </row>
@@ -966,10 +1030,52 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Thiết kế Event Schema phân tán chuẩn OpenTelemetry với trace_id, span_id, parent_span_id và HTTP status.
+- [1.5 điểm] Định nghĩa đầy đủ các trường ngữ cảnh chặng (hop.path, service_name, error attributes) xác định điểm gãy tại tool.
+- [1.5 điểm] Xây dựng phép truy vấn PromQL chính xác tính tỷ lệ lỗi 502 theo từng dịch vụ và phương pháp drilldown qua trace_id.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Lược đồ Sự kiện Phân tán (Distributed Tracing Event Schema - OpenTelemetry Standard):
+   - Cấu trúc bản ghi sự kiện JSON chuẩn hóa gắn cho từng bước chặng (Span Event):
+     ```json
+     {
+       "trace_id": "4bf92f3577b34da6a3ce929d0e0e4736",
+       "span_id": "00f067aa0ba902b7",
+       "parent_span_id": "5fb397be34d23b0f",
+       "service_name": "agent_worker",
+       "operation_name": "invoke_tool",
+       "timestamp_start": "2026-10-23T15:30:00.120000Z",
+       "timestamp_end": "2026-10-23T15:30:02.450000Z",
+       "duration_ms": 2330,
+       "status": {"code": "ERROR", "http_status": 502},
+       "attributes": {
+         "hop.order": 4,
+         "hop.path": "gateway -&gt; agent -&gt; model -&gt; tool",
+         "target.tool_name": "enterprise_database_query",
+         "error.type": "UpstreamConnectionRefused",
+         "error.message": "Tool endpoint returned HTTP 502 Bad Gateway due to connection timeout"
+       }
+     }
+     ```
+2. Phép Truy vấn Chỉ số Metric Xác định Nguồn gốc Lỗi 502 (PromQL Metrics Queries):
+   - Truy vấn 1: Xác định dịch vụ cụ thể phát sinh lỗi 502 đầu tiên trong chuỗi phân tán:
+     ```promql
+     sum by (service_name, target_endpoint) (
+       rate(http_requests_total{status="502"}[5m])
+     ) / sum by (service_name, target_endpoint) (
+       rate(http_requests_total[5m])
+     )
+     ```
+   - Truy vấn 2: Phân tích độ trễ P95 của các chặng dẫn tới lỗi 502:
+     ```promql
+     histogram_quantile(0.95, sum by (le, service_name) (
+       rate(http_request_duration_seconds_bucket{status="502"}[5m])
+     ))
+     ```
+   - Truy vết gốc rễ (Root Cause Drilldown): Khi dashboard cảnh báo tỷ lệ lỗi 502 tăng vọt ở tầng Gateway, kỹ sư tra cứu `trace_id` trên Jaeger/Tempo; lược đồ span chỉ rõ điểm gãy nằm tại chặng cuối `tool` bị mất kết nối, làm lan truyền mã lỗi 502 ngược dòng về Model, Agent và Gateway.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các hệ thống AI Agent nhiều tầng (Multi-Hop Agent Architecture), một mã lỗi 502 Bad Gateway tại cửa ngõ thường là hậu quả của sự cố ở mắt xích sâu nhất bên trong đồ thị gọi (như Tool hoặc Model). Việc áp dụng mô hình Distributed Tracing tuân thủ chuẩn OpenTelemetry kết hợp với các truy vấn PromQL phân tầng cho phép cô lập nguyên nhân gốc rễ chỉ trong vài giây.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Specification - Spans &amp; Trace Semantic Conventions: https://opentelemetry.io/docs/specs/otel/trace/semantic_conventions/ và Prometheus PromQL Basics</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1154,34 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Gắn nhãn chính xác 4 giai đoạn vòng đời từ PR CI, Tạo Digest D bất biến, Staging đến Production.
+- [1.5 điểm] Phân định rạch ròi cơ chế cổng kiểm duyệt: Cổng tự động cho Staging và Cổng phê duyệt thủ công có kiểm soát cho Production.
+- [1.5 điểm] Mô tả đường promotion tuân thủ nguyên tắc Build Once Deploy Everywhere (giữ nguyên Digest D) kèm lộ trình Canary.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Gắn Nhãn Các Giai đoạn và Ranh giới Pipeline (Stage Labeling Matrix):
+   - Giai đoạn 1 (Pull Request CI Verification Stage):
+     + Nhãn: `ci-validation` (Môi trường kiểm thử ephemeral trên nhánh PR).
+     + Thực thi: Linter, unit tests, security scans. Phê duyệt bắt buộc: Tối thiểu 2 Senior Engineers duyệt mã nguồn.
+   - Giai đoạn 2 (Immutable Artifact Creation Stage):
+     + Nhãn: `build-and-package` (Kích hoạt khi merge vào nhánh `main`).
+     + Thực thi: Build OCI Container Image một lần duy nhất, tạo ra mã băm bất biến `Digest D` (`image@sha256:...`). Ký số hình ảnh bằng Cosign/Sigstore.
+   - Giai đoạn 3 (Staging Environment Promotion Stage):
+     + Nhãn: `staging-deployment`.
+     + Cơ chế: Tự động hoàn toàn (Automated Gate). Ngay khi Digest D được tạo và vượt qua bài quét lỗ hổng nghiêm trọng (No High/Critical CVEs), image được deploy ngay lập tức lên cụm Staging để chạy Integration và End-to-End Test Suite.
+   - Giai đoạn 4 (Production Environment Promotion Stage):
+     + Nhãn: `production-deployment`.
+     + Cơ chế: Cổng phê duyệt thủ công kết hợp điều kiện tự động (Manual Approval &amp; Quality Gate).
+2. Mô tả Con đường Thăng cấp Bản phát hành (Promotion Pathway):
+   - Nguyên tắc Bất biến: 'Xây dựng Một lần, Triển khai Mọi nơi' (Build Once, Deploy Everywhere). Tuyệt đối cấm rebuild image khi thăng cấp từ Staging lên Production; chính xác Image Digest D đã được kiểm thử ở Staging sẽ được deploy lên Production.
+   - Điều kiện Tiên quyết để Mở Cổng Production:
+     + 100% các bài E2E test và Synthetic Canary trên Staging đạt kết quả PASS.
+     + Không phát hiện bất kỳ suy thoái độ trễ nào trong 2 giờ chạy thử trên Staging.
+     + Có văn bản phê duyệt điện tử (Electronic Sign-off) từ Release Manager / Tech Lead trên CI/CD console.
+   - Lộ trình Triển khai Production: Triển khai Canary 10% lưu lượng trong 30 phút -&gt; Nếu ổn định, tự động thăng cấp lên 100% toàn hệ thống.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy trình thăng cấp phần mềm (Artifact Promotion Pipeline) bảo đảm tính toàn vẹn tuyệt đối của chuỗi cung ứng phần mềm. Bằng việc khóa danh tính bằng mã băm Digest bất biến và thiết lập các cổng kiểm duyệt phân cấp (tự động cho Staging, kiểm soát chặt chẽ cho Production), doanh nghiệp loại trừ hoàn toàn nguy cơ sai lệch nhị phân giữa môi trường kiểm thử và môi trường thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Continuous Delivery Principles by Jez Humble and David Farley &amp; SLSA (Supply-chain Levels for Software Artifacts) Framework</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1260,61 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 5 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện trong bối cảnh rồi nối nó với một quyết định và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Thiết kế cấu trúc DAG chuẩn xác với các quan hệ phụ thuộc: lint và test chạy song song -&gt; build-image -&gt; deploy.
+- [2.0 điểm] Thực thi đầy đủ các ràng buộc bảo mật cho deploy: chỉ chạy trên main, sự kiện push tin cậy và pinned actions với full SHA hash.
+- [2.0 điểm] Mô tả toàn diện 4 nhánh rẽ khi có lỗi: lint fail, test fail, PR branch skipped deploy và untrusted fork isolation.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Dựng Đồ thị Có hướng Không chu trình (CI/CD Pipeline DAG Specification):
+   ```yaml
+   name: Secure Enterprise CI/CD Pipeline
+   on:
+     push:
+       branches: [ main ]
+     pull_request:
+       branches: [ main ]
+   jobs:
+     lint:
+       runs-on: ubuntu-latest
+       steps:
+         - uses: actions/checkout@b4ffde65f46336ab88eb53be808477a3936bae11 # Pinned full commit SHA
+         - name: Run Linters (Ruff / Flake8)
+           run: ruff check .
+     test:
+       runs-on: ubuntu-latest
+       steps:
+         - uses: actions/checkout@b4ffde65f46336ab88eb53be808477a3936bae11
+         - name: Run Test Suite (Pytest)
+           run: pytest tests/
+     build-image:
+       needs: [lint, test] # Phụ thuộc cả lint và test
+       runs-on: ubuntu-latest
+       steps:
+         - uses: actions/checkout@b4ffde65f46336ab88eb53be808477a3936bae11
+         - name: Build and Push OCI Image with Digest
+           run: docker build -t enterprise-agent:digest .
+     deploy:
+       needs: [build-image]
+       runs-on: ubuntu-latest
+       # Ràng buộc bảo mật nghiêm ngặt: Chỉ chạy trên main, trusted event và repository chính thức
+       if: github.ref == 'refs/heads/main' &amp;&amp; github.event_name == 'push' &amp;&amp; github.repository == 'enterprise/core-agent'
+       steps:
+         - uses: actions/checkout@b4ffde65f46336ab88eb53be808477a3936bae11
+         - name: Deploy to Cloud Production
+           run: ./scripts/deploy.sh
+   ```
+2. Mô tả Các Đường đi khi có Lỗi và Rẽ nhánh (Failure Paths &amp; Security Branching):
+   - Đường đi 1 (Lỗi Linting - Lint Failure Path):
+     Khi `lint` phát hiện vi phạm cú pháp -&gt; Job `lint` trả về exit code 1 (FAILED). Do `build-image` yêu cầu `needs: [lint, test]`, các job `build-image` và `deploy` lập tức bị HỦY BỎ (SKIPPED). Pipeline dừng lại ngay tại chốt kiểm soát đầu tiên.
+   - Đường đi 2 (Lỗi Kiểm thử - Test Failure Path):
+     Nếu `lint` thành công nhưng `test` thất bại (có unit test bị fail) -&gt; Job `test` bị FAILED. Job `build-image` bị SKIPPED, ngăn chặn tuyệt đối việc đóng gói mã nguồn lỗi thành image container.
+   - Đường đi 3 (Nhánh Pull Request An toàn - Non-Main Branch Path):
+     Khi một PR được mở từ feature branch: Các job `lint`, `test` và `build-image` được thực thi đầy đủ để kiểm tra chất lượng. Tuy nhiên, khi tới job `deploy`, điều kiện `if` đánh giá thấy `github.ref != 'refs/heads/main'` -&gt; Job `deploy` được ĐÁNH DẤU BỎ QUA (SKIPPED) một cách an toàn.
+   - Đường đi 4 (Sự kiện Không Tin cậy - Untrusted Fork Event Isolation):
+     Nếu kẻ tấn công gửi PR từ một fork repository bên ngoài nhằm kích hoạt deploy để đánh cắp secret, điều kiện `github.event_name == 'push'` và `github.repository` bảo đảm job `deploy` không bao giờ được phép khởi chạy.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bảo mật quy trình CI/CD là tuyến phòng thủ cốt tử chống lại các cuộc tấn công vào chuỗi cung ứng phần mềm (Software Supply Chain Attacks). Việc ghim cứng mã băm commit SHA cho các hành động bên thứ ba (Pinned Actions) loại bỏ rủi ro bị xâm nhập qua cập nhật tag giả mạo, trong khi việc ràng buộc điều kiện nhánh và sự kiện tin cậy ngăn chặn việc rò rỉ quyền triển khai sản xuất ra các môi trường không được kiểm soát.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+GitHub Actions Security Hardening Guide: https://docs.github.com/en/actions/security-guides/security-hardening-for-github-actions và OpenSSF Scorecard Standards</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1393,31 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc từng điều kiện rồi nối nó với giai đoạn chạy và phép kiểm có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Đọc từng điều kiện rồi nối nó với giai đoạn chạy và phép kiểm có thể quan sát.</t>
+- [1.0 điểm] Phân loại chính xác 3 bài kiểm tra vào 3 giai đoạn: Unit test (Pre-build), Build container (Build), Smoke test (Post-deploy).
+- [1.5 điểm] Chỉ ra chính xác nghịch lý logic của bài kiểm tra tự tham chiếu (workflow chưa kết thúc không thể có trạng thái success).
+- [1.5 điểm] Nêu giải pháp sửa triệt để: loại bỏ khỏi pipeline hiện tại, chuyển sang external cron monitor hoặc kiểm tra commit trước đó.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xếp Các Bài Kiểm tra vào Đúng Giai đoạn Vòng đời Pipeline (Test Phase Mapping):
+   - Giai đoạn 1: Giai đoạn Tiền Xây dựng (Pre-Build / CI Source Validation):
+     + Bài kiểm tra: `Unit Test dùng Mock`.
+     + Lý do: Chạy trực tiếp trên mã nguồn thô trong vài giây, sử dụng mock để cô lập các dịch vụ bên ngoài, kiểm tra logic thuật toán nội bộ trước khi tiêu tốn tài nguyên đóng gói.
+   - Giai đoạn 2: Giai đoạn Đóng gói (Build &amp; Packaging Stage):
+     + Tác vụ: `Build Container`.
+     + Lý do: Đóng gói mã nguồn và dependencies thành OCI Container Image, chạy bảo mật quét lỗ hổng lớp image.
+   - Giai đoạn 3: Giai đoạn Hậu Triển khai (Post-Deployment Verification Stage):
+     + Bài kiểm tra: `Smoke Test trên Public URL`.
+     + Lý do: Bắt buộc phải chạy SAU KHI container đã được triển khai lên môi trường chạy thực tế và endpoint công khai đã sẵn sàng nhận kết nối mạng.
+2. Phân tích Sai sót và Cách Sửa Bài Kiểm tra Tự Tham chiếu (Self-Referential Test Fix):
+   - Phân tích Sai sót (Chicken-and-Egg Flaw):
+     Bài kiểm tra kiểm tra badge hoặc trạng thái 'Success' của chính workflow khi bản thân workflow đó CÒN CHƯA HOÀN TẤT là một lỗi thiết kế nghiêm trọng về mặt logic (Self-Referential / Paradoxical Flaw). Tại thời điểm test đang chạy, trạng thái của workflow chỉ có thể là `in_progress` hoặc trạng thái của commit cũ; việc kỳ vọng nhận được trạng thái `success` của chính lần chạy hiện tại sẽ gây ra lỗi Fail giả tạo (False Negative) hoặc tạo ra vòng lặp bế tắc vô lý.
+   - Cách Sửa Triệt để (Architectural Remediation):
+     + Giải pháp Chuẩn mực: LOẠI BỎ HOÀN TOÀN bài test tự kiểm tra trạng thái khỏi chuỗi công việc của chính nó.
+     + Phương án Thay thế 1 (Asynchronous Status Badge Verification): Chuyển tác vụ kiểm tra hiển thị badge sang một Cron Job hoặc External Health Monitor độc lập chạy định kỳ bên ngoài pipeline.
+     + Phương án Thay thế 2 (Check Previous Commit Status): Nếu bắt buộc phải kiểm tra trong pipeline, chỉ kiểm tra trạng thái hoàn tất của lần chạy trước đó trên nhánh chính (`workflow_runs(status=completed, branch=main).conclusion == success`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thiết kế quy trình kiểm thử tự động đòi hỏi tính logic nhân quả nghiêm ngặt. Việc sắp xếp đúng thứ tự từ Unit Test (cô lập) đến Build (đóng gói) và Smoke Test (môi trường sống) bảo đảm tính hiệu quả của chu trình phản hồi. Loại bỏ các phép kiểm tra tự tham chiếu giải quyết các nghịch lý logic và ngăn chặn các báo động giả trong hệ thống CI/CD.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Testing Blog - Test Sizes &amp; Pipeline Ordering và Martin Fowler - Continuous Integration Guide</t>
         </is>
       </c>
     </row>
@@ -1294,10 +1496,27 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc cả ba tín hiệu: định danh, health và đường chức năng có xác thực; đừng kết luận từ một tín hiệu.
-Phân tích theo nguyên lý thiết kế: Đọc cả ba tín hiệu: định danh, health và đường chức năng có xác thực; đừng kết luận từ một tín hiệu.</t>
+- [1.0 điểm] Đưa ra quyết định chuẩn xác: Rollback khẩn cấp về bản D6 ngay lập tức dựa trên sự cố lỗi 500 nghiêm trọng.
+- [1.5 điểm] Phân tích toàn diện 3 tín hiệu đối lập: Phân biệt sự sai khác giữa shallow health check (200) và deep authenticated failure (500).
+- [1.5 điểm] Thiết lập bằng chứng kiểm toán đầy đủ: Log 3 tín hiệu, stacktrace lỗi của container D7 và bản ghi xác nhận rollback thành công về D6.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định Quản trị Bản phát hành (Release Governance Decision):
+   - QUYẾT ĐỊNH DỨT KHOÁT: TIẾN HÀNH ROLLBACK NGAY LẬP TỨC VỀ BẢN D6 (IMMEDIATE AUTOMATED ROLLBACK).
+   - Biện minh dựa trên đánh giá tổng thể ba tín hiệu:
+     + Tín hiệu 1 (Identity): Endpoint `/version` trả về đúng Digest D7 -&gt; Xác nhận việc triển khai kỹ thuật đã đưa đúng mã nhị phân mới lên hạ tầng.
+     + Tín hiệu 2 (Health Check): Endpoint `/health` trả về thành công -&gt; Đây chỉ là một phép kiểm tra nông (Shallow Liveness Check), chỉ chứng minh tiến trình web server còn sống, nhưng không phản ánh được chức năng thực tế.
+     + Tín hiệu 3 (Functional Execution): Yêu cầu tối thiểu có xác thực (Critical Authenticated Path) bị lỗi sập hoàn toàn với mã lỗi `HTTP 500 Internal Server Error` -&gt; Dịch vụ không thể phục vụ người dùng thực tế. Đây là sự cố nghiêm trọng cấp độ P1 (Blocking Severity); không thể giữ bản release D7 trong sản xuất.
+2. Thu thập và Ghi nhận Bằng chứng Kiểm toán Sự cố (Incident Audit Trail):
+   - Bằng chứng 1 (Bằng chứng Ba Tín hiệu Đối lập):
+     Lưu trữ bản ghi HTTP response song song: Lệnh gọi `/version` (Digest D7), lệnh gọi `/health` (HTTP 200) và lệnh gọi API có xác thực `curl -i -H 'Authorization: Bearer &lt;test_token&gt;' https://api.enterprise.com/v1/agent` trả về `HTTP/1.1 500 Internal Server Error` kèm Request Trace ID.
+   - Bằng chứng 2 (Nhật ký Truy vết Ngăn xếp Lỗi - Stacktrace Logs):
+     Trích xuất log lỗi từ container D7 tại thời điểm nhận request: Lưu lại toàn bộ traceback chi tiết (ví dụ: lỗi `KeyError: 'JWT_PUBLIC_KEY'` hoặc thiếu bảng migration mới).
+   - Bằng chứng 3 (Bản ghi Thao tác Hoàn tác - Rollback Audit Record):
+     Ghi nhật ký hệ thống: Thời điểm phát hiện sự cố, định danh người/hệ thống kích hoạt lệnh Rollback, thời gian hoàn tất chuyển hướng traffic về D6 (ví dụ: hoàn tất sau 12 giây), và xác nhận đường dẫn có xác thực trên D6 đã phục hồi trạng thái HTTP 200 hoàn hảo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong quy trình phát hành phần mềm hiện đại, việc một ứng dụng vượt qua bài kiểm tra sức khỏe nông (Shallow Health Check) không đồng nghĩa với việc ứng dụng hoạt động chính xác. Khi các luồng nghiệp vụ cốt lõi có xác thực gặp lỗi nghiêm trọng (HTTP 500), nguyên tắc 'Fail-Safe' yêu cầu kích hoạt hoàn tác khẩn cấp ngay lập tức để bảo vệ người dùng, đồng thời lưu giữ đầy đủ bằng chứng để phục vụ công tác điều tra nguyên nhân gốc rễ (Post-Mortem).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Postmortem Culture &amp; Incident Response: https://sre.google/sre-book/postmortem-culture/ và AWS Deployment Safety Best Practices</t>
         </is>
       </c>
     </row>
@@ -1382,10 +1601,35 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Lọc từng ứng viên theo policy trước; chỉ sau đó mới xét health hoặc chi phí.
-Phân tích theo nguyên lý thiết kế: Lọc từng ứng viên theo policy trước; chỉ sau đó mới xét health hoặc chi phí.</t>
+- [1.0 điểm] Phân tích chính sách lọc nghiêm ngặt: Loại F1 do vi phạm Data Region và loại F2 do cạn kiệt Budget Cap.
+- [1.5 điểm] Tính toán chính xác chuỗi failover: Primary (429) -&gt; F1 (bị chặn) -&gt; F2 (bị chặn) dẫn tới cạn kiệt toàn bộ routes hợp lệ.
+- [1.5 điểm] Xác định chuẩn xác hành vi ngắn mạch: Phản hồi mã HTTP 503 kèm lý do minh bạch và phát cảnh báo khẩn cấp cho SRE.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lọc và Đánh giá Ứng viên theo Chính sách Tuân thủ (Compliance &amp; Policy Filtering):
+   - Ứng viên Primary (Nhà cung cấp Chính):
+     + Đánh giá chính sách: Thỏa mãn hoàn toàn về pháp lý và ngân sách.
+     + Trạng thái kỹ thuật: BỊ RATE LIMIT (Mã lỗi HTTP 429) -&gt; Tạm thời không thể tiếp nhận cuộc gọi.
+   - Ứng viên F1 (Phương án Dự phòng 1):
+     + Trạng thái kỹ thuật: Đang hoạt động hoàn hảo (Healthy).
+     + Đánh giá chính sách: VI PHẠM CHÍNH SÁCH VÙNG DỮ LIỆU (Data Residency / Sovereignty Policy Violation - ví dụ: Dữ liệu bắt buộc lưu trữ tại EU nhưng F1 đặt tại US).
+     + Quyết định: LOẠI BỎ NGAY LẬP TỨC KHỎI DANH SÁCH ĐỊNH TUYẾN. Nguyên tắc tuân thủ pháp luật và an ninh dữ liệu là tuyệt đối; không bao giờ được phép vi phạm quy định chủ quyền dữ liệu chỉ để cứu vãn tính sẵn sàng của hệ thống.
+   - Ứng viên F2 (Phương án Dự phòng 2):
+     + Đánh giá chính sách dữ liệu: Tương thích hoàn toàn (đúng data region).
+     + Đánh giá chính sách tài chính: ĐÃ CHẠM TRẦN NGÂN SÁCH (Budget Cap Exhausted).
+     + Quyết định: LOẠI BỎ KHỎI DANH SÁCH ĐỊNH TUYẾN để bảo vệ doanh nghiệp khỏi nguy cơ thâm hụt tài chính.
+2. Tính toán Chuỗi Định tuyến / Chuyển hướng Dự phòng (Route &amp; Failover Pipeline):
+   - Trình tự đánh giá logic của hệ thống:
+     `Request -&gt; Thử nghiệm Primary (Nhận 429) -&gt; Đánh giá F1 (LOẠI BỎ do sai Data Region) -&gt; Đánh giá F2 (LOẠI BỎ do hết Budget) -&gt; KẾT THÚC: KHÔNG CÒN ROUTE HỢP LỆ NÀO KHẢ DỤNG.`
+3. Kết quả Xử lý khi Không Còn Route Hợp lệ (Terminal Exhaustion Handling):
+   - Hành vi Hệ thống: Ngắn mạch ngay lập tức (Fail-Fast Short Circuit), không gửi thêm bất kỳ request nào ra ngoài Internet.
+   - Phản hồi cho Người dùng: Trả về mã phản hồi `HTTP 503 Service Unavailable` hoặc `HTTP 429 Upstream Rate Limited`.
+   - Thân phản hồi JSON chi tiết:
+     `{"error": "service_unavailable", "reason": "Primary model rate limited and all fallback routes failed compliance/budget guardrails", "retry_after": 15}`.
+   - Cảnh báo Hệ thống: Phát tín hiệu cảnh báo mức độ khẩn cấp (P1 Alert) tới kênh trực vận hành của đội ngũ SRE để can thiệp nâng quota hoặc bổ sung ngân sách.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong thiết kế kiến trúc chuyển hướng dự phòng (Failover Architecture) cho các dịch vụ AI doanh nghiệp, các chốt chặn tuân thủ quy định (Compliance Guardrails như Chủ quyền Dữ liệu và Giới hạn Ngân sách) có độ ưu tiên cao hơn tính sẵn sàng kỹ thuật. Một giải pháp dự phòng dù khỏe mạnh về mặt mạng nhưng vi phạm pháp lý hoặc làm thủng ngân sách bắt buộc phải bị loại bỏ dứt khoát.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+AWS Well-Architected Framework - Reliability and Security Pillars &amp; GDPR Data Residency Compliance Guidelines</t>
         </is>
       </c>
     </row>
